--- a/checklist_forms/040_food_safety_checklist--checklist_forms.xlsx
+++ b/checklist_forms/040_food_safety_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'option1',_'label':_'option_1',_'value':_'value1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'option1', 'label': 'Option 1', 'value': 'value1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'option2',_'label':_'option_2',_'value':_'value2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'option2', 'label': 'Option 2', 'value': 'value2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'option3',_'label':_'option_3',_'value':_'value3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'option3', 'label': 'Option 3', 'value': 'value3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'option4',_'label':_'option_4',_'value':_'value4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'option4', 'label': 'Option 4', 'value': 'value4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'option5',_'label':_'option_5',_'value':_'value5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'option5', 'label': 'Option 5', 'value': 'value5'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'option6',_'label':_'option_6',_'value':_'value6'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'option6', 'label': 'Option 6', 'value': 'value6'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'option7',_'label':_'option_7',_'value':_'value7'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'option7', 'label': 'Option 7', 'value': 'value7'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'option8',_'label':_'option_8',_'value':_'value8'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'option8', 'label': 'Option 8', 'value': 'value8'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'option9',_'label':_'option_9',_'value':_'value9'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'option9', 'label': 'Option 9', 'value': 'value9'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_25,_'name':_'option10',_'label':_'option_10',_'value':_'value10'}</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 25, 'name': 'option10', 'label': 'Option 10', 'value': 'value10'}</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
